--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2018_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2018_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:51</t>
+    <t xml:space="preserve">2026-09-24 00:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2018_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2018_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:42</t>
+    <t xml:space="preserve">2026-10-01 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2018_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2018_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:16</t>
+    <t xml:space="preserve">2026-10-05 19:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
